--- a/docs/My_Personal_Reviews/18224049_UTS-5_Skor.xlsx
+++ b/docs/My_Personal_Reviews/18224049_UTS-5_Skor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\School\Algoritma dan Pemrogaman\all-about-me\My_Personal_Reviews\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D6CD6F-F8A1-4D91-BD67-5601604B9C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C815CA-B45E-4A72-B933-83D9E1815B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
